--- a/FM-MN-07_Crane no.1.xlsx
+++ b/FM-MN-07_Crane no.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59CE994-E022-4709-A838-FA74B7D75CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB8CE40-07D8-46DE-BDC8-BE9357AB80C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -430,25 +430,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -458,20 +454,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1525,80 +1525,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="18" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="27" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
+      <c r="W1" s="41"/>
+      <c r="X1" s="41"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="41"/>
+      <c r="AA1" s="41"/>
+      <c r="AB1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="28"/>
-      <c r="AE1" s="28"/>
-      <c r="AF1" s="28"/>
-      <c r="AG1" s="28"/>
+      <c r="AC1" s="41"/>
+      <c r="AD1" s="41"/>
+      <c r="AE1" s="41"/>
+      <c r="AF1" s="41"/>
+      <c r="AG1" s="41"/>
     </row>
     <row r="2" spans="1:33" s="18" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
-      <c r="V2" s="28"/>
-      <c r="W2" s="28"/>
-      <c r="X2" s="28"/>
-      <c r="Y2" s="28"/>
-      <c r="Z2" s="28"/>
-      <c r="AA2" s="28"/>
-      <c r="AB2" s="27" t="s">
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="41"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="41"/>
+      <c r="V2" s="41"/>
+      <c r="W2" s="41"/>
+      <c r="X2" s="41"/>
+      <c r="Y2" s="41"/>
+      <c r="Z2" s="41"/>
+      <c r="AA2" s="41"/>
+      <c r="AB2" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="AC2" s="28"/>
-      <c r="AD2" s="28"/>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="28"/>
-      <c r="AG2" s="28"/>
+      <c r="AC2" s="41"/>
+      <c r="AD2" s="41"/>
+      <c r="AE2" s="41"/>
+      <c r="AF2" s="41"/>
+      <c r="AG2" s="41"/>
     </row>
     <row r="3" spans="1:33" s="18" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="21"/>
@@ -1639,46 +1639,46 @@
       <c r="A4" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="38" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="38"/>
-      <c r="AB4" s="38"/>
-      <c r="AC4" s="38"/>
-      <c r="AD4" s="38"/>
-      <c r="AE4" s="38"/>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="39"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="36"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="36"/>
+      <c r="AE4" s="36"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="37"/>
     </row>
     <row r="5" spans="1:33" s="12" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="30"/>
-      <c r="B5" s="41"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="39"/>
       <c r="C5" s="17">
         <v>1</v>
       </c>
@@ -2078,139 +2078,139 @@
     <row r="14" spans="1:33" ht="22.5" customHeight="1">
       <c r="A14" s="11"/>
       <c r="B14" s="10"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="29"/>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="29"/>
-      <c r="R14" s="29"/>
-      <c r="S14" s="29"/>
-      <c r="T14" s="29"/>
-      <c r="U14" s="29"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="30"/>
+      <c r="Q14" s="30"/>
+      <c r="R14" s="30"/>
+      <c r="S14" s="30"/>
+      <c r="T14" s="30"/>
+      <c r="U14" s="30"/>
       <c r="V14" s="35"/>
-      <c r="W14" s="29"/>
-      <c r="X14" s="29"/>
-      <c r="Y14" s="29"/>
-      <c r="Z14" s="29"/>
-      <c r="AA14" s="29"/>
-      <c r="AB14" s="29"/>
-      <c r="AC14" s="29"/>
-      <c r="AD14" s="29"/>
-      <c r="AE14" s="29"/>
-      <c r="AF14" s="29"/>
-      <c r="AG14" s="29"/>
+      <c r="W14" s="30"/>
+      <c r="X14" s="30"/>
+      <c r="Y14" s="30"/>
+      <c r="Z14" s="30"/>
+      <c r="AA14" s="30"/>
+      <c r="AB14" s="30"/>
+      <c r="AC14" s="30"/>
+      <c r="AD14" s="30"/>
+      <c r="AE14" s="30"/>
+      <c r="AF14" s="30"/>
+      <c r="AG14" s="30"/>
     </row>
     <row r="15" spans="1:33" ht="22.5" customHeight="1">
       <c r="B15" s="9"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
-      <c r="P15" s="30"/>
-      <c r="Q15" s="30"/>
-      <c r="R15" s="30"/>
-      <c r="S15" s="30"/>
-      <c r="T15" s="30"/>
-      <c r="U15" s="30"/>
-      <c r="V15" s="30"/>
-      <c r="W15" s="30"/>
-      <c r="X15" s="30"/>
-      <c r="Y15" s="30"/>
-      <c r="Z15" s="30"/>
-      <c r="AA15" s="30"/>
-      <c r="AB15" s="30"/>
-      <c r="AC15" s="30"/>
-      <c r="AD15" s="30"/>
-      <c r="AE15" s="30"/>
-      <c r="AF15" s="30"/>
-      <c r="AG15" s="30"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="29"/>
+      <c r="W15" s="29"/>
+      <c r="X15" s="29"/>
+      <c r="Y15" s="29"/>
+      <c r="Z15" s="29"/>
+      <c r="AA15" s="29"/>
+      <c r="AB15" s="29"/>
+      <c r="AC15" s="29"/>
+      <c r="AD15" s="29"/>
+      <c r="AE15" s="29"/>
+      <c r="AF15" s="29"/>
+      <c r="AG15" s="29"/>
     </row>
     <row r="16" spans="1:33" ht="22.5" customHeight="1">
       <c r="B16" s="9"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="31"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="31"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="31"/>
-      <c r="T16" s="31"/>
-      <c r="U16" s="31"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="28"/>
       <c r="V16" s="34"/>
-      <c r="W16" s="31"/>
-      <c r="X16" s="31"/>
-      <c r="Y16" s="31"/>
-      <c r="Z16" s="31"/>
-      <c r="AA16" s="31"/>
-      <c r="AB16" s="31"/>
-      <c r="AC16" s="31"/>
-      <c r="AD16" s="31"/>
-      <c r="AE16" s="31"/>
-      <c r="AF16" s="31"/>
-      <c r="AG16" s="31"/>
+      <c r="W16" s="28"/>
+      <c r="X16" s="28"/>
+      <c r="Y16" s="28"/>
+      <c r="Z16" s="28"/>
+      <c r="AA16" s="28"/>
+      <c r="AB16" s="28"/>
+      <c r="AC16" s="28"/>
+      <c r="AD16" s="28"/>
+      <c r="AE16" s="28"/>
+      <c r="AF16" s="28"/>
+      <c r="AG16" s="28"/>
     </row>
     <row r="17" spans="2:33" ht="22.5" customHeight="1">
       <c r="B17" s="9"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="30"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="30"/>
-      <c r="R17" s="30"/>
-      <c r="S17" s="30"/>
-      <c r="T17" s="30"/>
-      <c r="U17" s="30"/>
-      <c r="V17" s="30"/>
-      <c r="W17" s="30"/>
-      <c r="X17" s="30"/>
-      <c r="Y17" s="30"/>
-      <c r="Z17" s="30"/>
-      <c r="AA17" s="30"/>
-      <c r="AB17" s="30"/>
-      <c r="AC17" s="30"/>
-      <c r="AD17" s="30"/>
-      <c r="AE17" s="30"/>
-      <c r="AF17" s="30"/>
-      <c r="AG17" s="30"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="29"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="29"/>
+      <c r="W17" s="29"/>
+      <c r="X17" s="29"/>
+      <c r="Y17" s="29"/>
+      <c r="Z17" s="29"/>
+      <c r="AA17" s="29"/>
+      <c r="AB17" s="29"/>
+      <c r="AC17" s="29"/>
+      <c r="AD17" s="29"/>
+      <c r="AE17" s="29"/>
+      <c r="AF17" s="29"/>
+      <c r="AG17" s="29"/>
     </row>
     <row r="18" spans="2:33" ht="19.5" customHeight="1">
       <c r="B18" s="8" t="s">
@@ -2218,26 +2218,57 @@
       </c>
     </row>
     <row r="19" spans="2:33" ht="342.75" customHeight="1">
-      <c r="B19" s="26"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="43"/>
+      <c r="M19" s="43"/>
+      <c r="N19" s="43"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="43"/>
+      <c r="R19" s="43"/>
+      <c r="S19" s="43"/>
+      <c r="T19" s="43"/>
+      <c r="U19" s="43"/>
+      <c r="V19" s="43"/>
+      <c r="W19" s="43"/>
+      <c r="X19" s="43"/>
+      <c r="Y19" s="43"/>
+      <c r="Z19" s="43"/>
+      <c r="AA19" s="43"/>
+      <c r="AB19" s="43"/>
+      <c r="AC19" s="43"/>
+      <c r="AD19" s="43"/>
+      <c r="AE19" s="43"/>
+      <c r="AF19" s="43"/>
+      <c r="AG19" s="43"/>
     </row>
     <row r="20" spans="2:33" ht="23.25" customHeight="1"/>
     <row r="21" spans="2:33" ht="21" customHeight="1">
       <c r="AA21" s="7"/>
       <c r="AB21" s="7"/>
-      <c r="AC21" s="42"/>
-      <c r="AD21" s="43"/>
-      <c r="AE21" s="43"/>
-      <c r="AF21" s="43"/>
-      <c r="AG21" s="43"/>
+      <c r="AC21" s="31"/>
+      <c r="AD21" s="32"/>
+      <c r="AE21" s="32"/>
+      <c r="AF21" s="32"/>
+      <c r="AG21" s="32"/>
     </row>
     <row r="22" spans="2:33" ht="29.25" customHeight="1">
-      <c r="AC22" s="36" t="s">
+      <c r="AC22" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="AD22" s="37"/>
-      <c r="AE22" s="37"/>
-      <c r="AF22" s="37"/>
-      <c r="AG22" s="37"/>
+      <c r="AD22" s="27"/>
+      <c r="AE22" s="27"/>
+      <c r="AF22" s="27"/>
+      <c r="AG22" s="27"/>
     </row>
     <row r="23" spans="2:33" ht="14.25" customHeight="1">
       <c r="B23" s="6"/>
@@ -2262,7 +2293,62 @@
       <c r="B68" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="70">
+  <mergeCells count="71">
+    <mergeCell ref="B19:AG19"/>
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="AD14:AD15"/>
+    <mergeCell ref="AC16:AC17"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="T14:T15"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="AG16:AG17"/>
+    <mergeCell ref="A1:AA2"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="AB16:AB17"/>
+    <mergeCell ref="R16:R17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="AF16:AF17"/>
+    <mergeCell ref="O16:O17"/>
+    <mergeCell ref="U16:U17"/>
+    <mergeCell ref="W16:W17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="AF14:AF15"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="P16:P17"/>
+    <mergeCell ref="AC14:AC15"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="AD16:AD17"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="U14:U15"/>
+    <mergeCell ref="W14:W15"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="V16:V17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="V14:V15"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="AE16:AE17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="AE14:AE15"/>
+    <mergeCell ref="N14:N15"/>
     <mergeCell ref="AC22:AG22"/>
     <mergeCell ref="Q16:Q17"/>
     <mergeCell ref="G16:G17"/>
@@ -2279,60 +2365,6 @@
     <mergeCell ref="AC21:AG21"/>
     <mergeCell ref="R14:R15"/>
     <mergeCell ref="AB14:AB15"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="V16:V17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="V14:V15"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="L16:L17"/>
-    <mergeCell ref="AE16:AE17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="AE14:AE15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="AF14:AF15"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="P16:P17"/>
-    <mergeCell ref="AC14:AC15"/>
-    <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="AD16:AD17"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="U14:U15"/>
-    <mergeCell ref="W14:W15"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="AB16:AB17"/>
-    <mergeCell ref="R16:R17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="AF16:AF17"/>
-    <mergeCell ref="O16:O17"/>
-    <mergeCell ref="U16:U17"/>
-    <mergeCell ref="W16:W17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="AD14:AD15"/>
-    <mergeCell ref="AC16:AC17"/>
-    <mergeCell ref="N16:N17"/>
-    <mergeCell ref="Q14:Q15"/>
-    <mergeCell ref="S14:S15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="T14:T15"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="AG16:AG17"/>
-    <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="K14:K15"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>

--- a/FM-MN-07_Crane no.1.xlsx
+++ b/FM-MN-07_Crane no.1.xlsx
@@ -335,7 +335,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -443,6 +443,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1779,8 +1782,16 @@
       <c r="AB6" s="13" t="n"/>
       <c r="AC6" s="13" t="n"/>
       <c r="AD6" s="13" t="n"/>
-      <c r="AE6" s="13" t="n"/>
-      <c r="AF6" s="13" t="n"/>
+      <c r="AE6" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF6" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG6" s="13" t="n"/>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="12">
@@ -1820,8 +1831,16 @@
       <c r="AB7" s="13" t="n"/>
       <c r="AC7" s="13" t="n"/>
       <c r="AD7" s="13" t="n"/>
-      <c r="AE7" s="13" t="n"/>
-      <c r="AF7" s="13" t="n"/>
+      <c r="AE7" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF7" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG7" s="13" t="n"/>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="12">
@@ -1862,8 +1881,16 @@
       <c r="AB8" s="13" t="n"/>
       <c r="AC8" s="13" t="n"/>
       <c r="AD8" s="13" t="n"/>
-      <c r="AE8" s="13" t="n"/>
-      <c r="AF8" s="13" t="n"/>
+      <c r="AE8" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF8" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG8" s="13" t="n"/>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="12">
@@ -1903,8 +1930,16 @@
       <c r="AB9" s="13" t="n"/>
       <c r="AC9" s="13" t="n"/>
       <c r="AD9" s="13" t="n"/>
-      <c r="AE9" s="13" t="n"/>
-      <c r="AF9" s="13" t="n"/>
+      <c r="AE9" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF9" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG9" s="13" t="n"/>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="12">
@@ -1945,8 +1980,16 @@
       <c r="AB10" s="13" t="n"/>
       <c r="AC10" s="13" t="n"/>
       <c r="AD10" s="13" t="n"/>
-      <c r="AE10" s="13" t="n"/>
-      <c r="AF10" s="13" t="n"/>
+      <c r="AE10" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF10" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG10" s="13" t="n"/>
     </row>
     <row r="11" ht="15.75" customFormat="1" customHeight="1" s="12">
@@ -1986,8 +2029,16 @@
       <c r="AB11" s="13" t="n"/>
       <c r="AC11" s="13" t="n"/>
       <c r="AD11" s="13" t="n"/>
-      <c r="AE11" s="13" t="n"/>
-      <c r="AF11" s="13" t="n"/>
+      <c r="AE11" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF11" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AG11" s="13" t="n"/>
     </row>
     <row r="12" ht="15.75" customFormat="1" customHeight="1" s="12">
@@ -2089,8 +2140,16 @@
       <c r="AB14" s="30" t="n"/>
       <c r="AC14" s="30" t="n"/>
       <c r="AD14" s="30" t="n"/>
-      <c r="AE14" s="30" t="n"/>
-      <c r="AF14" s="30" t="n"/>
+      <c r="AE14" s="35" t="inlineStr">
+        <is>
+          <t>นายอดุลย์  ศิริรัตน์</t>
+        </is>
+      </c>
+      <c r="AF14" s="35" t="inlineStr">
+        <is>
+          <t>นายอดุลย์  ศิริรัตน์</t>
+        </is>
+      </c>
       <c r="AG14" s="30" t="n"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
@@ -2203,7 +2262,11 @@
       </c>
     </row>
     <row r="19" ht="342.75" customHeight="1">
-      <c r="B19" s="43" t="n"/>
+      <c r="B19" s="44" t="inlineStr">
+        <is>
+          <t>[วันที่ 29]: สายสลิงเครนตัวเล็กมีการบิดงอ, เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟ,  [วันที่ 30]: สายสลิงเครนตัวเล็กมีการบิดงอ, เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="23.25" customHeight="1"/>
     <row r="21" ht="21" customHeight="1">

--- a/FM-MN-07_Crane no.1.xlsx
+++ b/FM-MN-07_Crane no.1.xlsx
@@ -1792,7 +1792,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG6" s="13" t="n"/>
+      <c r="AG6" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="12">
       <c r="A7" s="15" t="n">
@@ -1841,7 +1845,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG7" s="13" t="n"/>
+      <c r="AG7" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="12">
       <c r="A8" s="15" t="n">
@@ -1891,7 +1899,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG8" s="13" t="n"/>
+      <c r="AG8" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="12">
       <c r="A9" s="15" t="n">
@@ -1940,7 +1952,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG9" s="13" t="n"/>
+      <c r="AG9" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="12">
       <c r="A10" s="15" t="n">
@@ -1990,7 +2006,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG10" s="13" t="n"/>
+      <c r="AG10" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15.75" customFormat="1" customHeight="1" s="12">
       <c r="A11" s="15" t="n">
@@ -2039,7 +2059,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AG11" s="13" t="n"/>
+      <c r="AG11" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15.75" customFormat="1" customHeight="1" s="12">
       <c r="A12" s="15" t="n"/>
@@ -2150,7 +2174,11 @@
           <t>นายอดุลย์  ศิริรัตน์</t>
         </is>
       </c>
-      <c r="AG14" s="30" t="n"/>
+      <c r="AG14" s="35" t="inlineStr">
+        <is>
+          <t>นายอดุลย์  ศิริรัตน์</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="B15" s="9" t="n"/>
@@ -2264,7 +2292,7 @@
     <row r="19" ht="342.75" customHeight="1">
       <c r="B19" s="44" t="inlineStr">
         <is>
-          <t>[วันที่ 29]: สายสลิงเครนตัวเล็กมีการบิดงอ, เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟ,  [วันที่ 30]: สายสลิงเครนตัวเล็กมีการบิดงอ, เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด</t>
+          <t>[วันที่ 29]: สายสลิงเครนตัวเล็กมีการบิดงอ, เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟ,  [วันที่ 30]: สายสลิงเครนตัวเล็กมีการบิดงอ, เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด,  [วันที่ 31]: สายสลิงเครนตัวเล็กมีการบิดงอ, เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด</t>
         </is>
       </c>
     </row>

--- a/FM-MN-07_Crane no.1.xlsx
+++ b/FM-MN-07_Crane no.1.xlsx
@@ -1754,49 +1754,37 @@
           <t>ตรวจเช็คปุ่มกดต้องอยู่ในสภาพพร้อมใช้งาน ไม่แตก ไม่ชำรุด เสียหาย</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="13" t="n"/>
-      <c r="H6" s="13" t="n"/>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="13" t="n"/>
-      <c r="K6" s="13" t="n"/>
-      <c r="L6" s="13" t="n"/>
-      <c r="M6" s="13" t="n"/>
-      <c r="N6" s="13" t="n"/>
-      <c r="O6" s="13" t="n"/>
-      <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="13" t="n"/>
-      <c r="R6" s="13" t="n"/>
-      <c r="S6" s="13" t="n"/>
-      <c r="T6" s="13" t="n"/>
-      <c r="U6" s="13" t="n"/>
-      <c r="V6" s="13" t="n"/>
-      <c r="W6" s="13" t="n"/>
-      <c r="X6" s="13" t="n"/>
-      <c r="Y6" s="13" t="n"/>
-      <c r="Z6" s="13" t="n"/>
-      <c r="AA6" s="13" t="n"/>
-      <c r="AB6" s="13" t="n"/>
-      <c r="AC6" s="13" t="n"/>
-      <c r="AD6" s="13" t="n"/>
-      <c r="AE6" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF6" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG6" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C6" s="13" t="inlineStr"/>
+      <c r="D6" s="13" t="inlineStr"/>
+      <c r="E6" s="13" t="inlineStr"/>
+      <c r="F6" s="13" t="inlineStr"/>
+      <c r="G6" s="13" t="inlineStr"/>
+      <c r="H6" s="13" t="inlineStr"/>
+      <c r="I6" s="13" t="inlineStr"/>
+      <c r="J6" s="13" t="inlineStr"/>
+      <c r="K6" s="13" t="inlineStr"/>
+      <c r="L6" s="13" t="inlineStr"/>
+      <c r="M6" s="13" t="inlineStr"/>
+      <c r="N6" s="13" t="inlineStr"/>
+      <c r="O6" s="13" t="inlineStr"/>
+      <c r="P6" s="13" t="inlineStr"/>
+      <c r="Q6" s="13" t="inlineStr"/>
+      <c r="R6" s="13" t="inlineStr"/>
+      <c r="S6" s="13" t="inlineStr"/>
+      <c r="T6" s="13" t="inlineStr"/>
+      <c r="U6" s="13" t="inlineStr"/>
+      <c r="V6" s="13" t="inlineStr"/>
+      <c r="W6" s="13" t="inlineStr"/>
+      <c r="X6" s="13" t="inlineStr"/>
+      <c r="Y6" s="13" t="inlineStr"/>
+      <c r="Z6" s="13" t="inlineStr"/>
+      <c r="AA6" s="13" t="inlineStr"/>
+      <c r="AB6" s="13" t="inlineStr"/>
+      <c r="AC6" s="13" t="inlineStr"/>
+      <c r="AD6" s="13" t="inlineStr"/>
+      <c r="AE6" s="13" t="inlineStr"/>
+      <c r="AF6" s="13" t="inlineStr"/>
+      <c r="AG6" s="13" t="inlineStr"/>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="12">
       <c r="A7" s="15" t="n">
@@ -1807,49 +1795,37 @@
           <t>ตรวจเช็คการหยุดเครน เดินหน้า และถอยหลัง เมื่อปล่อยปุ่มกดต้องหยุดทันที</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="13" t="n"/>
-      <c r="H7" s="13" t="n"/>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="13" t="n"/>
-      <c r="K7" s="13" t="n"/>
-      <c r="L7" s="13" t="n"/>
-      <c r="M7" s="13" t="n"/>
-      <c r="N7" s="13" t="n"/>
-      <c r="O7" s="13" t="n"/>
-      <c r="P7" s="13" t="n"/>
-      <c r="Q7" s="13" t="n"/>
-      <c r="R7" s="13" t="n"/>
-      <c r="S7" s="13" t="n"/>
-      <c r="T7" s="13" t="n"/>
-      <c r="U7" s="13" t="n"/>
-      <c r="V7" s="13" t="n"/>
-      <c r="W7" s="13" t="n"/>
-      <c r="X7" s="13" t="n"/>
-      <c r="Y7" s="13" t="n"/>
-      <c r="Z7" s="13" t="n"/>
-      <c r="AA7" s="13" t="n"/>
-      <c r="AB7" s="13" t="n"/>
-      <c r="AC7" s="13" t="n"/>
-      <c r="AD7" s="13" t="n"/>
-      <c r="AE7" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF7" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG7" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C7" s="13" t="inlineStr"/>
+      <c r="D7" s="13" t="inlineStr"/>
+      <c r="E7" s="13" t="inlineStr"/>
+      <c r="F7" s="13" t="inlineStr"/>
+      <c r="G7" s="13" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr"/>
+      <c r="I7" s="13" t="inlineStr"/>
+      <c r="J7" s="13" t="inlineStr"/>
+      <c r="K7" s="13" t="inlineStr"/>
+      <c r="L7" s="13" t="inlineStr"/>
+      <c r="M7" s="13" t="inlineStr"/>
+      <c r="N7" s="13" t="inlineStr"/>
+      <c r="O7" s="13" t="inlineStr"/>
+      <c r="P7" s="13" t="inlineStr"/>
+      <c r="Q7" s="13" t="inlineStr"/>
+      <c r="R7" s="13" t="inlineStr"/>
+      <c r="S7" s="13" t="inlineStr"/>
+      <c r="T7" s="13" t="inlineStr"/>
+      <c r="U7" s="13" t="inlineStr"/>
+      <c r="V7" s="13" t="inlineStr"/>
+      <c r="W7" s="13" t="inlineStr"/>
+      <c r="X7" s="13" t="inlineStr"/>
+      <c r="Y7" s="13" t="inlineStr"/>
+      <c r="Z7" s="13" t="inlineStr"/>
+      <c r="AA7" s="13" t="inlineStr"/>
+      <c r="AB7" s="13" t="inlineStr"/>
+      <c r="AC7" s="13" t="inlineStr"/>
+      <c r="AD7" s="13" t="inlineStr"/>
+      <c r="AE7" s="13" t="inlineStr"/>
+      <c r="AF7" s="13" t="inlineStr"/>
+      <c r="AG7" s="13" t="inlineStr"/>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="12">
       <c r="A8" s="15" t="n">
@@ -1861,49 +1837,37 @@
 และบิดงอ</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="13" t="n"/>
-      <c r="H8" s="13" t="n"/>
-      <c r="I8" s="13" t="n"/>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="13" t="n"/>
-      <c r="M8" s="13" t="n"/>
-      <c r="N8" s="13" t="n"/>
-      <c r="O8" s="13" t="n"/>
-      <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="13" t="n"/>
-      <c r="R8" s="13" t="n"/>
-      <c r="S8" s="13" t="n"/>
-      <c r="T8" s="13" t="n"/>
-      <c r="U8" s="13" t="n"/>
-      <c r="V8" s="13" t="n"/>
-      <c r="W8" s="13" t="n"/>
-      <c r="X8" s="13" t="n"/>
-      <c r="Y8" s="13" t="n"/>
-      <c r="Z8" s="13" t="n"/>
-      <c r="AA8" s="13" t="n"/>
-      <c r="AB8" s="13" t="n"/>
-      <c r="AC8" s="13" t="n"/>
-      <c r="AD8" s="13" t="n"/>
-      <c r="AE8" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF8" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG8" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C8" s="13" t="inlineStr"/>
+      <c r="D8" s="13" t="inlineStr"/>
+      <c r="E8" s="13" t="inlineStr"/>
+      <c r="F8" s="13" t="inlineStr"/>
+      <c r="G8" s="13" t="inlineStr"/>
+      <c r="H8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr"/>
+      <c r="J8" s="13" t="inlineStr"/>
+      <c r="K8" s="13" t="inlineStr"/>
+      <c r="L8" s="13" t="inlineStr"/>
+      <c r="M8" s="13" t="inlineStr"/>
+      <c r="N8" s="13" t="inlineStr"/>
+      <c r="O8" s="13" t="inlineStr"/>
+      <c r="P8" s="13" t="inlineStr"/>
+      <c r="Q8" s="13" t="inlineStr"/>
+      <c r="R8" s="13" t="inlineStr"/>
+      <c r="S8" s="13" t="inlineStr"/>
+      <c r="T8" s="13" t="inlineStr"/>
+      <c r="U8" s="13" t="inlineStr"/>
+      <c r="V8" s="13" t="inlineStr"/>
+      <c r="W8" s="13" t="inlineStr"/>
+      <c r="X8" s="13" t="inlineStr"/>
+      <c r="Y8" s="13" t="inlineStr"/>
+      <c r="Z8" s="13" t="inlineStr"/>
+      <c r="AA8" s="13" t="inlineStr"/>
+      <c r="AB8" s="13" t="inlineStr"/>
+      <c r="AC8" s="13" t="inlineStr"/>
+      <c r="AD8" s="13" t="inlineStr"/>
+      <c r="AE8" s="13" t="inlineStr"/>
+      <c r="AF8" s="13" t="inlineStr"/>
+      <c r="AG8" s="13" t="inlineStr"/>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="12">
       <c r="A9" s="15" t="n">
@@ -1914,49 +1878,37 @@
           <t>ตรวจเช็คตะขอต้องไม่มีรอยแตกร้าวสูญหายกิ๊ปปากตะขอไม่ชำรุดหรือหลุดหาย</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="13" t="n"/>
-      <c r="I9" s="13" t="n"/>
-      <c r="J9" s="13" t="n"/>
-      <c r="K9" s="13" t="n"/>
-      <c r="L9" s="13" t="n"/>
-      <c r="M9" s="13" t="n"/>
-      <c r="N9" s="13" t="n"/>
-      <c r="O9" s="13" t="n"/>
-      <c r="P9" s="13" t="n"/>
-      <c r="Q9" s="13" t="n"/>
-      <c r="R9" s="13" t="n"/>
-      <c r="S9" s="13" t="n"/>
-      <c r="T9" s="13" t="n"/>
-      <c r="U9" s="13" t="n"/>
-      <c r="V9" s="13" t="n"/>
-      <c r="W9" s="13" t="n"/>
-      <c r="X9" s="13" t="n"/>
-      <c r="Y9" s="13" t="n"/>
-      <c r="Z9" s="13" t="n"/>
-      <c r="AA9" s="13" t="n"/>
-      <c r="AB9" s="13" t="n"/>
-      <c r="AC9" s="13" t="n"/>
-      <c r="AD9" s="13" t="n"/>
-      <c r="AE9" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF9" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG9" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C9" s="13" t="inlineStr"/>
+      <c r="D9" s="13" t="inlineStr"/>
+      <c r="E9" s="13" t="inlineStr"/>
+      <c r="F9" s="13" t="inlineStr"/>
+      <c r="G9" s="13" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr"/>
+      <c r="I9" s="13" t="inlineStr"/>
+      <c r="J9" s="13" t="inlineStr"/>
+      <c r="K9" s="13" t="inlineStr"/>
+      <c r="L9" s="13" t="inlineStr"/>
+      <c r="M9" s="13" t="inlineStr"/>
+      <c r="N9" s="13" t="inlineStr"/>
+      <c r="O9" s="13" t="inlineStr"/>
+      <c r="P9" s="13" t="inlineStr"/>
+      <c r="Q9" s="13" t="inlineStr"/>
+      <c r="R9" s="13" t="inlineStr"/>
+      <c r="S9" s="13" t="inlineStr"/>
+      <c r="T9" s="13" t="inlineStr"/>
+      <c r="U9" s="13" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="W9" s="13" t="inlineStr"/>
+      <c r="X9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="Z9" s="13" t="inlineStr"/>
+      <c r="AA9" s="13" t="inlineStr"/>
+      <c r="AB9" s="13" t="inlineStr"/>
+      <c r="AC9" s="13" t="inlineStr"/>
+      <c r="AD9" s="13" t="inlineStr"/>
+      <c r="AE9" s="13" t="inlineStr"/>
+      <c r="AF9" s="13" t="inlineStr"/>
+      <c r="AG9" s="13" t="inlineStr"/>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="12">
       <c r="A10" s="15" t="n">
@@ -1968,49 +1920,37 @@
 ไม่เรียบร้อย</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="13" t="n"/>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="13" t="n"/>
-      <c r="L10" s="13" t="n"/>
-      <c r="M10" s="13" t="n"/>
-      <c r="N10" s="13" t="n"/>
-      <c r="O10" s="13" t="n"/>
-      <c r="P10" s="13" t="n"/>
-      <c r="Q10" s="13" t="n"/>
-      <c r="R10" s="13" t="n"/>
-      <c r="S10" s="13" t="n"/>
-      <c r="T10" s="13" t="n"/>
-      <c r="U10" s="13" t="n"/>
-      <c r="V10" s="13" t="n"/>
-      <c r="W10" s="13" t="n"/>
-      <c r="X10" s="13" t="n"/>
-      <c r="Y10" s="13" t="n"/>
-      <c r="Z10" s="13" t="n"/>
-      <c r="AA10" s="13" t="n"/>
-      <c r="AB10" s="13" t="n"/>
-      <c r="AC10" s="13" t="n"/>
-      <c r="AD10" s="13" t="n"/>
-      <c r="AE10" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF10" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG10" s="13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C10" s="13" t="inlineStr"/>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr"/>
+      <c r="F10" s="13" t="inlineStr"/>
+      <c r="G10" s="13" t="inlineStr"/>
+      <c r="H10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr"/>
+      <c r="J10" s="13" t="inlineStr"/>
+      <c r="K10" s="13" t="inlineStr"/>
+      <c r="L10" s="13" t="inlineStr"/>
+      <c r="M10" s="13" t="inlineStr"/>
+      <c r="N10" s="13" t="inlineStr"/>
+      <c r="O10" s="13" t="inlineStr"/>
+      <c r="P10" s="13" t="inlineStr"/>
+      <c r="Q10" s="13" t="inlineStr"/>
+      <c r="R10" s="13" t="inlineStr"/>
+      <c r="S10" s="13" t="inlineStr"/>
+      <c r="T10" s="13" t="inlineStr"/>
+      <c r="U10" s="13" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="W10" s="13" t="inlineStr"/>
+      <c r="X10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="Z10" s="13" t="inlineStr"/>
+      <c r="AA10" s="13" t="inlineStr"/>
+      <c r="AB10" s="13" t="inlineStr"/>
+      <c r="AC10" s="13" t="inlineStr"/>
+      <c r="AD10" s="13" t="inlineStr"/>
+      <c r="AE10" s="13" t="inlineStr"/>
+      <c r="AF10" s="13" t="inlineStr"/>
+      <c r="AG10" s="13" t="inlineStr"/>
     </row>
     <row r="11" ht="15.75" customFormat="1" customHeight="1" s="12">
       <c r="A11" s="15" t="n">
@@ -2021,49 +1961,37 @@
           <t>ตรวจเช็คสัญญานเสียงเมื่อเริ่มเดินเครนต้องมีเสียงเตือนการทำงาน</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="13" t="n"/>
-      <c r="I11" s="13" t="n"/>
-      <c r="J11" s="13" t="n"/>
-      <c r="K11" s="13" t="n"/>
-      <c r="L11" s="13" t="n"/>
-      <c r="M11" s="13" t="n"/>
-      <c r="N11" s="13" t="n"/>
-      <c r="O11" s="13" t="n"/>
-      <c r="P11" s="13" t="n"/>
-      <c r="Q11" s="13" t="n"/>
-      <c r="R11" s="13" t="n"/>
-      <c r="S11" s="13" t="n"/>
-      <c r="T11" s="13" t="n"/>
-      <c r="U11" s="13" t="n"/>
-      <c r="V11" s="13" t="n"/>
-      <c r="W11" s="13" t="n"/>
-      <c r="X11" s="13" t="n"/>
-      <c r="Y11" s="13" t="n"/>
-      <c r="Z11" s="13" t="n"/>
-      <c r="AA11" s="13" t="n"/>
-      <c r="AB11" s="13" t="n"/>
-      <c r="AC11" s="13" t="n"/>
-      <c r="AD11" s="13" t="n"/>
-      <c r="AE11" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AF11" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AG11" s="13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="C11" s="13" t="inlineStr"/>
+      <c r="D11" s="13" t="inlineStr"/>
+      <c r="E11" s="13" t="inlineStr"/>
+      <c r="F11" s="13" t="inlineStr"/>
+      <c r="G11" s="13" t="inlineStr"/>
+      <c r="H11" s="13" t="inlineStr"/>
+      <c r="I11" s="13" t="inlineStr"/>
+      <c r="J11" s="13" t="inlineStr"/>
+      <c r="K11" s="13" t="inlineStr"/>
+      <c r="L11" s="13" t="inlineStr"/>
+      <c r="M11" s="13" t="inlineStr"/>
+      <c r="N11" s="13" t="inlineStr"/>
+      <c r="O11" s="13" t="inlineStr"/>
+      <c r="P11" s="13" t="inlineStr"/>
+      <c r="Q11" s="13" t="inlineStr"/>
+      <c r="R11" s="13" t="inlineStr"/>
+      <c r="S11" s="13" t="inlineStr"/>
+      <c r="T11" s="13" t="inlineStr"/>
+      <c r="U11" s="13" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="W11" s="13" t="inlineStr"/>
+      <c r="X11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="Z11" s="13" t="inlineStr"/>
+      <c r="AA11" s="13" t="inlineStr"/>
+      <c r="AB11" s="13" t="inlineStr"/>
+      <c r="AC11" s="13" t="inlineStr"/>
+      <c r="AD11" s="13" t="inlineStr"/>
+      <c r="AE11" s="13" t="inlineStr"/>
+      <c r="AF11" s="13" t="inlineStr"/>
+      <c r="AG11" s="13" t="inlineStr"/>
     </row>
     <row r="12" ht="15.75" customFormat="1" customHeight="1" s="12">
       <c r="A12" s="15" t="n"/>
@@ -2136,49 +2064,37 @@
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="11" t="n"/>
       <c r="B14" s="10" t="n"/>
-      <c r="C14" s="30" t="n"/>
-      <c r="D14" s="30" t="n"/>
-      <c r="E14" s="30" t="n"/>
-      <c r="F14" s="30" t="n"/>
-      <c r="G14" s="30" t="n"/>
-      <c r="H14" s="30" t="n"/>
-      <c r="I14" s="30" t="n"/>
-      <c r="J14" s="30" t="n"/>
-      <c r="K14" s="30" t="n"/>
-      <c r="L14" s="30" t="n"/>
-      <c r="M14" s="30" t="n"/>
-      <c r="N14" s="30" t="n"/>
-      <c r="O14" s="30" t="n"/>
-      <c r="P14" s="30" t="n"/>
-      <c r="Q14" s="30" t="n"/>
-      <c r="R14" s="30" t="n"/>
-      <c r="S14" s="30" t="n"/>
-      <c r="T14" s="30" t="n"/>
-      <c r="U14" s="30" t="n"/>
-      <c r="V14" s="35" t="n"/>
-      <c r="W14" s="30" t="n"/>
-      <c r="X14" s="30" t="n"/>
-      <c r="Y14" s="30" t="n"/>
-      <c r="Z14" s="30" t="n"/>
-      <c r="AA14" s="30" t="n"/>
-      <c r="AB14" s="30" t="n"/>
-      <c r="AC14" s="30" t="n"/>
-      <c r="AD14" s="30" t="n"/>
-      <c r="AE14" s="35" t="inlineStr">
-        <is>
-          <t>นายอดุลย์  ศิริรัตน์</t>
-        </is>
-      </c>
-      <c r="AF14" s="35" t="inlineStr">
-        <is>
-          <t>นายอดุลย์  ศิริรัตน์</t>
-        </is>
-      </c>
-      <c r="AG14" s="35" t="inlineStr">
-        <is>
-          <t>นายอดุลย์  ศิริรัตน์</t>
-        </is>
-      </c>
+      <c r="C14" s="30" t="inlineStr"/>
+      <c r="D14" s="30" t="inlineStr"/>
+      <c r="E14" s="30" t="inlineStr"/>
+      <c r="F14" s="30" t="inlineStr"/>
+      <c r="G14" s="30" t="inlineStr"/>
+      <c r="H14" s="30" t="inlineStr"/>
+      <c r="I14" s="30" t="inlineStr"/>
+      <c r="J14" s="30" t="inlineStr"/>
+      <c r="K14" s="30" t="inlineStr"/>
+      <c r="L14" s="30" t="inlineStr"/>
+      <c r="M14" s="30" t="inlineStr"/>
+      <c r="N14" s="30" t="inlineStr"/>
+      <c r="O14" s="30" t="inlineStr"/>
+      <c r="P14" s="30" t="inlineStr"/>
+      <c r="Q14" s="30" t="inlineStr"/>
+      <c r="R14" s="30" t="inlineStr"/>
+      <c r="S14" s="30" t="inlineStr"/>
+      <c r="T14" s="30" t="inlineStr"/>
+      <c r="U14" s="30" t="inlineStr"/>
+      <c r="V14" s="35" t="inlineStr"/>
+      <c r="W14" s="30" t="inlineStr"/>
+      <c r="X14" s="30" t="inlineStr"/>
+      <c r="Y14" s="30" t="inlineStr"/>
+      <c r="Z14" s="30" t="inlineStr"/>
+      <c r="AA14" s="30" t="inlineStr"/>
+      <c r="AB14" s="30" t="inlineStr"/>
+      <c r="AC14" s="30" t="inlineStr"/>
+      <c r="AD14" s="30" t="inlineStr"/>
+      <c r="AE14" s="35" t="inlineStr"/>
+      <c r="AF14" s="35" t="inlineStr"/>
+      <c r="AG14" s="35" t="inlineStr"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="B15" s="9" t="n"/>
@@ -2216,37 +2132,37 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="B16" s="9" t="n"/>
-      <c r="C16" s="28" t="n"/>
-      <c r="D16" s="28" t="n"/>
-      <c r="E16" s="28" t="n"/>
-      <c r="F16" s="28" t="n"/>
-      <c r="G16" s="28" t="n"/>
-      <c r="H16" s="28" t="n"/>
-      <c r="I16" s="28" t="n"/>
-      <c r="J16" s="28" t="n"/>
-      <c r="K16" s="28" t="n"/>
-      <c r="L16" s="28" t="n"/>
-      <c r="M16" s="28" t="n"/>
-      <c r="N16" s="28" t="n"/>
-      <c r="O16" s="28" t="n"/>
-      <c r="P16" s="28" t="n"/>
-      <c r="Q16" s="28" t="n"/>
-      <c r="R16" s="28" t="n"/>
-      <c r="S16" s="28" t="n"/>
-      <c r="T16" s="28" t="n"/>
-      <c r="U16" s="28" t="n"/>
-      <c r="V16" s="34" t="n"/>
-      <c r="W16" s="28" t="n"/>
-      <c r="X16" s="28" t="n"/>
-      <c r="Y16" s="28" t="n"/>
-      <c r="Z16" s="28" t="n"/>
-      <c r="AA16" s="28" t="n"/>
-      <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="28" t="n"/>
-      <c r="AD16" s="28" t="n"/>
-      <c r="AE16" s="28" t="n"/>
-      <c r="AF16" s="28" t="n"/>
-      <c r="AG16" s="28" t="n"/>
+      <c r="C16" s="28" t="inlineStr"/>
+      <c r="D16" s="28" t="inlineStr"/>
+      <c r="E16" s="28" t="inlineStr"/>
+      <c r="F16" s="28" t="inlineStr"/>
+      <c r="G16" s="28" t="inlineStr"/>
+      <c r="H16" s="28" t="inlineStr"/>
+      <c r="I16" s="28" t="inlineStr"/>
+      <c r="J16" s="28" t="inlineStr"/>
+      <c r="K16" s="28" t="inlineStr"/>
+      <c r="L16" s="28" t="inlineStr"/>
+      <c r="M16" s="28" t="inlineStr"/>
+      <c r="N16" s="28" t="inlineStr"/>
+      <c r="O16" s="28" t="inlineStr"/>
+      <c r="P16" s="28" t="inlineStr"/>
+      <c r="Q16" s="28" t="inlineStr"/>
+      <c r="R16" s="28" t="inlineStr"/>
+      <c r="S16" s="28" t="inlineStr"/>
+      <c r="T16" s="28" t="inlineStr"/>
+      <c r="U16" s="28" t="inlineStr"/>
+      <c r="V16" s="34" t="inlineStr"/>
+      <c r="W16" s="28" t="inlineStr"/>
+      <c r="X16" s="28" t="inlineStr"/>
+      <c r="Y16" s="28" t="inlineStr"/>
+      <c r="Z16" s="28" t="inlineStr"/>
+      <c r="AA16" s="28" t="inlineStr"/>
+      <c r="AB16" s="28" t="inlineStr"/>
+      <c r="AC16" s="28" t="inlineStr"/>
+      <c r="AD16" s="28" t="inlineStr"/>
+      <c r="AE16" s="28" t="inlineStr"/>
+      <c r="AF16" s="28" t="inlineStr"/>
+      <c r="AG16" s="28" t="inlineStr"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="B17" s="9" t="n"/>
@@ -2290,11 +2206,7 @@
       </c>
     </row>
     <row r="19" ht="342.75" customHeight="1">
-      <c r="B19" s="44" t="inlineStr">
-        <is>
-          <t>[วันที่ 29]: สายสลิงเครนตัวเล็กมีการบิดงอ, เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟ,  [วันที่ 30]: สายสลิงเครนตัวเล็กมีการบิดงอ, เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด,  [วันที่ 31]: สายสลิงเครนตัวเล็กมีการบิดงอ, เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด</t>
-        </is>
-      </c>
+      <c r="B19" s="44" t="inlineStr"/>
     </row>
     <row r="20" ht="23.25" customHeight="1"/>
     <row r="21" ht="21" customHeight="1">

--- a/FM-MN-07_Crane no.1.xlsx
+++ b/FM-MN-07_Crane no.1.xlsx
@@ -1759,7 +1759,11 @@
       <c r="E6" s="13" t="inlineStr"/>
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="inlineStr"/>
-      <c r="H6" s="13" t="inlineStr"/>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I6" s="13" t="inlineStr"/>
       <c r="J6" s="13" t="inlineStr"/>
       <c r="K6" s="13" t="inlineStr"/>
@@ -1800,7 +1804,11 @@
       <c r="E7" s="13" t="inlineStr"/>
       <c r="F7" s="13" t="inlineStr"/>
       <c r="G7" s="13" t="inlineStr"/>
-      <c r="H7" s="13" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I7" s="13" t="inlineStr"/>
       <c r="J7" s="13" t="inlineStr"/>
       <c r="K7" s="13" t="inlineStr"/>
@@ -1842,7 +1850,11 @@
       <c r="E8" s="13" t="inlineStr"/>
       <c r="F8" s="13" t="inlineStr"/>
       <c r="G8" s="13" t="inlineStr"/>
-      <c r="H8" s="13" t="inlineStr"/>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I8" s="13" t="inlineStr"/>
       <c r="J8" s="13" t="inlineStr"/>
       <c r="K8" s="13" t="inlineStr"/>
@@ -1883,7 +1895,11 @@
       <c r="E9" s="13" t="inlineStr"/>
       <c r="F9" s="13" t="inlineStr"/>
       <c r="G9" s="13" t="inlineStr"/>
-      <c r="H9" s="13" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I9" s="13" t="inlineStr"/>
       <c r="J9" s="13" t="inlineStr"/>
       <c r="K9" s="13" t="inlineStr"/>
@@ -1925,7 +1941,11 @@
       <c r="E10" s="13" t="inlineStr"/>
       <c r="F10" s="13" t="inlineStr"/>
       <c r="G10" s="13" t="inlineStr"/>
-      <c r="H10" s="13" t="inlineStr"/>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I10" s="13" t="inlineStr"/>
       <c r="J10" s="13" t="inlineStr"/>
       <c r="K10" s="13" t="inlineStr"/>
@@ -1966,7 +1986,11 @@
       <c r="E11" s="13" t="inlineStr"/>
       <c r="F11" s="13" t="inlineStr"/>
       <c r="G11" s="13" t="inlineStr"/>
-      <c r="H11" s="13" t="inlineStr"/>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I11" s="13" t="inlineStr"/>
       <c r="J11" s="13" t="inlineStr"/>
       <c r="K11" s="13" t="inlineStr"/>
@@ -2069,7 +2093,11 @@
       <c r="E14" s="30" t="inlineStr"/>
       <c r="F14" s="30" t="inlineStr"/>
       <c r="G14" s="30" t="inlineStr"/>
-      <c r="H14" s="30" t="inlineStr"/>
+      <c r="H14" s="35" t="inlineStr">
+        <is>
+          <t>นายอดุลย์  ศิริรัตน์</t>
+        </is>
+      </c>
       <c r="I14" s="30" t="inlineStr"/>
       <c r="J14" s="30" t="inlineStr"/>
       <c r="K14" s="30" t="inlineStr"/>
@@ -2206,7 +2234,11 @@
       </c>
     </row>
     <row r="19" ht="342.75" customHeight="1">
-      <c r="B19" s="44" t="inlineStr"/>
+      <c r="B19" s="44" t="inlineStr">
+        <is>
+          <t>[วันที่ 6]: ข้อ 3: สายสลิงเครนตัวเล็กมีการบิดงอ, ข้อ 6: เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="23.25" customHeight="1"/>
     <row r="21" ht="21" customHeight="1">

--- a/FM-MN-07_Crane no.1.xlsx
+++ b/FM-MN-07_Crane no.1.xlsx
@@ -1764,7 +1764,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr"/>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J6" s="13" t="inlineStr"/>
       <c r="K6" s="13" t="inlineStr"/>
       <c r="L6" s="13" t="inlineStr"/>
@@ -1809,7 +1813,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I7" s="13" t="inlineStr"/>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J7" s="13" t="inlineStr"/>
       <c r="K7" s="13" t="inlineStr"/>
       <c r="L7" s="13" t="inlineStr"/>
@@ -1855,7 +1863,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J8" s="13" t="inlineStr"/>
       <c r="K8" s="13" t="inlineStr"/>
       <c r="L8" s="13" t="inlineStr"/>
@@ -1900,7 +1912,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I9" s="13" t="inlineStr"/>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J9" s="13" t="inlineStr"/>
       <c r="K9" s="13" t="inlineStr"/>
       <c r="L9" s="13" t="inlineStr"/>
@@ -1946,7 +1962,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J10" s="13" t="inlineStr"/>
       <c r="K10" s="13" t="inlineStr"/>
       <c r="L10" s="13" t="inlineStr"/>
@@ -1991,7 +2011,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I11" s="13" t="inlineStr"/>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J11" s="13" t="inlineStr"/>
       <c r="K11" s="13" t="inlineStr"/>
       <c r="L11" s="13" t="inlineStr"/>
@@ -2098,7 +2122,11 @@
           <t>นายอดุลย์  ศิริรัตน์</t>
         </is>
       </c>
-      <c r="I14" s="30" t="inlineStr"/>
+      <c r="I14" s="35" t="inlineStr">
+        <is>
+          <t>นายอดุลย์  ศิริรัตน์</t>
+        </is>
+      </c>
       <c r="J14" s="30" t="inlineStr"/>
       <c r="K14" s="30" t="inlineStr"/>
       <c r="L14" s="30" t="inlineStr"/>
@@ -2236,7 +2264,7 @@
     <row r="19" ht="342.75" customHeight="1">
       <c r="B19" s="44" t="inlineStr">
         <is>
-          <t>[วันที่ 6]: ข้อ 3: สายสลิงเครนตัวเล็กมีการบิดงอ, ข้อ 6: เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด</t>
+          <t>[วันที่ 6]: ข้อ 3: สายสลิงเครนตัวเล็กมีการบิดงอ, ข้อ 6: เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด,  [วันที่ 7]: ข้อ 3: สายสลิงเครนตัวเล็กมีการบิดงอ, ข้อ 6: เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด</t>
         </is>
       </c>
     </row>

--- a/FM-MN-07_Crane no.1.xlsx
+++ b/FM-MN-07_Crane no.1.xlsx
@@ -1769,7 +1769,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J6" s="13" t="inlineStr"/>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K6" s="13" t="inlineStr"/>
       <c r="L6" s="13" t="inlineStr"/>
       <c r="M6" s="13" t="inlineStr"/>
@@ -1818,7 +1822,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J7" s="13" t="inlineStr"/>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K7" s="13" t="inlineStr"/>
       <c r="L7" s="13" t="inlineStr"/>
       <c r="M7" s="13" t="inlineStr"/>
@@ -1868,7 +1876,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J8" s="13" t="inlineStr"/>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K8" s="13" t="inlineStr"/>
       <c r="L8" s="13" t="inlineStr"/>
       <c r="M8" s="13" t="inlineStr"/>
@@ -1917,7 +1929,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr"/>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K9" s="13" t="inlineStr"/>
       <c r="L9" s="13" t="inlineStr"/>
       <c r="M9" s="13" t="inlineStr"/>
@@ -1967,7 +1983,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr"/>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K10" s="13" t="inlineStr"/>
       <c r="L10" s="13" t="inlineStr"/>
       <c r="M10" s="13" t="inlineStr"/>
@@ -2016,7 +2036,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="J11" s="13" t="inlineStr"/>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="K11" s="13" t="inlineStr"/>
       <c r="L11" s="13" t="inlineStr"/>
       <c r="M11" s="13" t="inlineStr"/>
@@ -2127,7 +2151,11 @@
           <t>นายอดุลย์  ศิริรัตน์</t>
         </is>
       </c>
-      <c r="J14" s="30" t="inlineStr"/>
+      <c r="J14" s="35" t="inlineStr">
+        <is>
+          <t>นายอดุลย์  ศิริรัตน์</t>
+        </is>
+      </c>
       <c r="K14" s="30" t="inlineStr"/>
       <c r="L14" s="30" t="inlineStr"/>
       <c r="M14" s="30" t="inlineStr"/>
@@ -2264,7 +2292,7 @@
     <row r="19" ht="342.75" customHeight="1">
       <c r="B19" s="44" t="inlineStr">
         <is>
-          <t>[วันที่ 6]: ข้อ 3: สายสลิงเครนตัวเล็กมีการบิดงอ, ข้อ 6: เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด,  [วันที่ 7]: ข้อ 3: สายสลิงเครนตัวเล็กมีการบิดงอ, ข้อ 6: เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด</t>
+          <t>[วันที่ 6]: ข้อ 3: สายสลิงเครนตัวเล็กมีการบิดงอ, ข้อ 6: เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด,  [วันที่ 7]: ข้อ 3: สายสลิงเครนตัวเล็กมีการบิดงอ, ข้อ 6: เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด,  [วันที่ 8]: ข้อ 3: สายสลิงเครนตัวเล็กมีการบิดงอ, ข้อ 6: เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด</t>
         </is>
       </c>
     </row>

--- a/FM-MN-07_Crane no.1.xlsx
+++ b/FM-MN-07_Crane no.1.xlsx
@@ -1775,7 +1775,11 @@
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr"/>
-      <c r="L6" s="13" t="inlineStr"/>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M6" s="13" t="inlineStr"/>
       <c r="N6" s="13" t="inlineStr"/>
       <c r="O6" s="13" t="inlineStr"/>
@@ -1828,7 +1832,11 @@
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr"/>
-      <c r="L7" s="13" t="inlineStr"/>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M7" s="13" t="inlineStr"/>
       <c r="N7" s="13" t="inlineStr"/>
       <c r="O7" s="13" t="inlineStr"/>
@@ -1882,7 +1890,11 @@
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr"/>
-      <c r="L8" s="13" t="inlineStr"/>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M8" s="13" t="inlineStr"/>
       <c r="N8" s="13" t="inlineStr"/>
       <c r="O8" s="13" t="inlineStr"/>
@@ -1935,7 +1947,11 @@
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr"/>
-      <c r="L9" s="13" t="inlineStr"/>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M9" s="13" t="inlineStr"/>
       <c r="N9" s="13" t="inlineStr"/>
       <c r="O9" s="13" t="inlineStr"/>
@@ -1989,7 +2005,11 @@
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr"/>
-      <c r="L10" s="13" t="inlineStr"/>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M10" s="13" t="inlineStr"/>
       <c r="N10" s="13" t="inlineStr"/>
       <c r="O10" s="13" t="inlineStr"/>
@@ -2042,7 +2062,11 @@
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr"/>
-      <c r="L11" s="13" t="inlineStr"/>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="M11" s="13" t="inlineStr"/>
       <c r="N11" s="13" t="inlineStr"/>
       <c r="O11" s="13" t="inlineStr"/>
@@ -2157,7 +2181,11 @@
         </is>
       </c>
       <c r="K14" s="30" t="inlineStr"/>
-      <c r="L14" s="30" t="inlineStr"/>
+      <c r="L14" s="35" t="inlineStr">
+        <is>
+          <t>นายอดุลย์  ศิริรัตน์</t>
+        </is>
+      </c>
       <c r="M14" s="30" t="inlineStr"/>
       <c r="N14" s="30" t="inlineStr"/>
       <c r="O14" s="30" t="inlineStr"/>
@@ -2292,7 +2320,7 @@
     <row r="19" ht="342.75" customHeight="1">
       <c r="B19" s="44" t="inlineStr">
         <is>
-          <t>[วันที่ 6]: ข้อ 3: สายสลิงเครนตัวเล็กมีการบิดงอ, ข้อ 6: เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด,  [วันที่ 7]: ข้อ 3: สายสลิงเครนตัวเล็กมีการบิดงอ, ข้อ 6: เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด,  [วันที่ 8]: ข้อ 3: สายสลิงเครนตัวเล็กมีการบิดงอ, ข้อ 6: เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด</t>
+          <t>[วันที่ 6]: ข้อ 3: สายสลิงเครนตัวเล็กมีการบิดงอ, ข้อ 6: เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด,  [วันที่ 7]: ข้อ 3: สายสลิงเครนตัวเล็กมีการบิดงอ, ข้อ 6: เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด,  [วันที่ 8]: ข้อ 3: สายสลิงเครนตัวเล็กมีการบิดงอ, ข้อ 6: เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด,  [วันที่ 10]: ข้อ 3: สายสลิงเครนตัวเล็กมีการบิดงอ, ข้อ 6: เสียงสัญญาณเตือนไม่ดังมีแค่สัญญาณไฟและเครนตัวเล็กมีเสียงดังเวลากดขึ้นสุด</t>
         </is>
       </c>
     </row>
